--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754474893_individual_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008510362272481009</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>39825075</v>
+        <v>4103143</v>
       </c>
       <c r="L2" t="n">
-        <v>21855651</v>
+        <v>1804254</v>
       </c>
       <c r="M2" t="n">
-        <v>5072701</v>
+        <v>345239</v>
       </c>
       <c r="N2" t="n">
-        <v>233692</v>
+        <v>7029</v>
       </c>
       <c r="O2" t="n">
-        <v>3002758</v>
+        <v>166506</v>
       </c>
       <c r="P2" t="n">
-        <v>1145413</v>
+        <v>57582</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999961256980896</v>
+        <v>0.999773383140564</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8583200573921204</v>
+        <v>0.7458970546722412</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7345041632652283</v>
+        <v>0.5705374479293823</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6788108348846436</v>
+        <v>0.4454535841941833</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2412147670984268</v>
+        <v>0.04740068316459656</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7206476926803589</v>
+        <v>0.4875967502593994</v>
       </c>
       <c r="W2" t="n">
-        <v>0.827373206615448</v>
+        <v>0.6613755226135254</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002038439189791413</v>
       </c>
       <c r="C3" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="D3" t="n">
-        <v>39825075</v>
+        <v>4103143</v>
       </c>
       <c r="E3" t="n">
-        <v>5153362</v>
+        <v>840884</v>
       </c>
       <c r="F3" t="n">
-        <v>118522</v>
+        <v>27834</v>
       </c>
       <c r="G3" t="n">
-        <v>11415</v>
+        <v>2269</v>
       </c>
       <c r="H3" t="n">
-        <v>6584</v>
+        <v>1177</v>
       </c>
       <c r="I3" t="n">
-        <v>431</v>
+        <v>125</v>
       </c>
       <c r="J3" t="n">
-        <v>90147396</v>
+        <v>10015191</v>
       </c>
       <c r="K3" t="n">
-        <v>95276985</v>
+        <v>9956137</v>
       </c>
       <c r="L3" t="n">
-        <v>109576211</v>
+        <v>11665154</v>
       </c>
       <c r="M3" t="n">
-        <v>136155481</v>
+        <v>14959932</v>
       </c>
       <c r="N3" t="n">
-        <v>145427523</v>
+        <v>16098643</v>
       </c>
       <c r="O3" t="n">
-        <v>141213888</v>
+        <v>15643242</v>
       </c>
       <c r="P3" t="n">
-        <v>144986608</v>
+        <v>16106432</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8827334642410278</v>
+        <v>0.8246437907218933</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7411160469055176</v>
+        <v>0.5456978678703308</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6031249165534973</v>
+        <v>0.3673228025436401</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2907499372959137</v>
+        <v>0.07836382836103439</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6544064879417419</v>
+        <v>0.3256006836891174</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6579777598381042</v>
+        <v>0.2972956299781799</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03213413144859563</v>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>6130660</v>
+        <v>1274261</v>
       </c>
       <c r="E4" t="n">
-        <v>21855651</v>
+        <v>1804254</v>
       </c>
       <c r="F4" t="n">
-        <v>1286588</v>
+        <v>188444</v>
       </c>
       <c r="G4" t="n">
-        <v>84707</v>
+        <v>16661</v>
       </c>
       <c r="H4" t="n">
-        <v>121200</v>
+        <v>20299</v>
       </c>
       <c r="I4" t="n">
-        <v>11327</v>
+        <v>2385</v>
       </c>
       <c r="J4" t="n">
-        <v>2202</v>
+        <v>1431</v>
       </c>
       <c r="K4" t="n">
-        <v>6573787</v>
+        <v>1397808</v>
       </c>
       <c r="L4" t="n">
-        <v>7900001</v>
+        <v>1358122</v>
       </c>
       <c r="M4" t="n">
-        <v>2400222</v>
+        <v>429789</v>
       </c>
       <c r="N4" t="n">
-        <v>735121</v>
+        <v>141260</v>
       </c>
       <c r="O4" t="n">
-        <v>1163991</v>
+        <v>174977</v>
       </c>
       <c r="P4" t="n">
-        <v>238984</v>
+        <v>29482</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999980628490448</v>
+        <v>0.999886691570282</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8703555464744568</v>
+        <v>0.7832962274551392</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7377952933311462</v>
+        <v>0.5578413009643555</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6387336254119873</v>
+        <v>0.4026328921318054</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2636760473251343</v>
+        <v>0.05907069891691208</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6859316229820251</v>
+        <v>0.3904631733894348</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7330162525177002</v>
+        <v>0.4102012515068054</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>278</v>
+        <v>228</v>
       </c>
       <c r="D5" t="n">
-        <v>309677</v>
+        <v>91634</v>
       </c>
       <c r="E5" t="n">
-        <v>2265033</v>
+        <v>403276</v>
       </c>
       <c r="F5" t="n">
-        <v>5072701</v>
+        <v>345239</v>
       </c>
       <c r="G5" t="n">
-        <v>231982</v>
+        <v>35931</v>
       </c>
       <c r="H5" t="n">
-        <v>483808</v>
+        <v>55424</v>
       </c>
       <c r="I5" t="n">
-        <v>47218</v>
+        <v>8147</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5290553</v>
+        <v>872512</v>
       </c>
       <c r="L5" t="n">
-        <v>7634537</v>
+        <v>1502070</v>
       </c>
       <c r="M5" t="n">
-        <v>3337996</v>
+        <v>594640</v>
       </c>
       <c r="N5" t="n">
-        <v>570064</v>
+        <v>82668</v>
       </c>
       <c r="O5" t="n">
-        <v>1585763</v>
+        <v>344875</v>
       </c>
       <c r="P5" t="n">
-        <v>595395</v>
+        <v>136104</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999850392341614</v>
+        <v>0.9999123811721802</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9192717671394348</v>
+        <v>0.860969066619873</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8942987322807312</v>
+        <v>0.8248461484909058</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9609555602073669</v>
+        <v>0.9372655153274536</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9911191463470459</v>
+        <v>0.986286997795105</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9812899231910706</v>
+        <v>0.9681650400161743</v>
       </c>
       <c r="W5" t="n">
-        <v>0.994322657585144</v>
+        <v>0.9898597598075867</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>112235</v>
+        <v>21064</v>
       </c>
       <c r="E6" t="n">
-        <v>195146</v>
+        <v>26130</v>
       </c>
       <c r="F6" t="n">
-        <v>181185</v>
+        <v>28024</v>
       </c>
       <c r="G6" t="n">
-        <v>233692</v>
+        <v>7029</v>
       </c>
       <c r="H6" t="n">
-        <v>74355</v>
+        <v>6497</v>
       </c>
       <c r="I6" t="n">
-        <v>7071</v>
+        <v>921</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>451</v>
+        <v>266</v>
       </c>
       <c r="D7" t="n">
-        <v>20275</v>
+        <v>10177</v>
       </c>
       <c r="E7" t="n">
-        <v>264587</v>
+        <v>79714</v>
       </c>
       <c r="F7" t="n">
-        <v>760645</v>
+        <v>165588</v>
       </c>
       <c r="G7" t="n">
-        <v>366868</v>
+        <v>71226</v>
       </c>
       <c r="H7" t="n">
-        <v>3002758</v>
+        <v>166506</v>
       </c>
       <c r="I7" t="n">
-        <v>172937</v>
+        <v>17904</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1107</v>
+        <v>662</v>
       </c>
       <c r="D8" t="n">
-        <v>940</v>
+        <v>672</v>
       </c>
       <c r="E8" t="n">
-        <v>21873</v>
+        <v>8118</v>
       </c>
       <c r="F8" t="n">
-        <v>53282</v>
+        <v>19899</v>
       </c>
       <c r="G8" t="n">
-        <v>40149</v>
+        <v>15173</v>
       </c>
       <c r="H8" t="n">
-        <v>478044</v>
+        <v>91580</v>
       </c>
       <c r="I8" t="n">
-        <v>1145413</v>
+        <v>57582</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
